--- a/artfynd/A 27795-2025 artfynd.xlsx
+++ b/artfynd/A 27795-2025 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>106959641</v>
+        <v>106959640</v>
       </c>
       <c r="B2" t="n">
-        <v>107008</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>110078</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,16 +686,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220320</v>
+        <v>220299</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ängsskära</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Serratula tinctoria</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -710,17 +705,17 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -729,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>546783.5885636851</v>
+        <v>546798</v>
       </c>
       <c r="R2" t="n">
-        <v>6474524.297264613</v>
+        <v>6474537</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -762,19 +757,9 @@
           <t>2022-07-17</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-07-17</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -805,15 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>106959640</v>
+        <v>106959641</v>
       </c>
       <c r="B3" t="n">
-        <v>106964</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>110117</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -821,16 +801,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220299</v>
+        <v>220320</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Ängsskära</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Serratula tinctoria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -840,17 +820,17 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -859,10 +839,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>546798.1359238111</v>
+        <v>546783</v>
       </c>
       <c r="R3" t="n">
-        <v>6474537.046470855</v>
+        <v>6474524</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -892,19 +872,9 @@
           <t>2022-07-17</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2022-07-17</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
